--- a/src_files/data_files/demanddata_other.xlsx
+++ b/src_files/data_files/demanddata_other.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-master\north_european_model\src_files\data_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{013D8619-5D33-44DA-BEFB-D3B8044F004A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14224AA-D665-407F-97C3-F667F4292B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Readme" sheetId="2" r:id="rId1"/>
-    <sheet name="demanddata_other demands" sheetId="1" r:id="rId2"/>
+    <sheet name="demanddata_other demands" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'demanddata_other demands'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'demanddata_other demands'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="26">
   <si>
     <t>Scenario</t>
   </si>
@@ -111,131 +110,10 @@
     <t>Node_suffix</t>
   </si>
   <si>
-    <t>Updated version of annual demands for Northern European model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The code processes multiple demand files by:
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          2. Merging sheets into a single DataFrame.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          3. Checking for duplicate entries based on key columns.</t>
-  </si>
-  <si>
-    <t>Mandatory columns:</t>
-  </si>
-  <si>
-    <t>E.g. FI00</t>
-  </si>
-  <si>
-    <t>Modelled energy carrier, e.g. electricity, heat, H2</t>
-  </si>
-  <si>
-    <t>Additional identifier used when creating the node name, see below</t>
-  </si>
-  <si>
-    <t>scenario identifier, e.g. National Trends</t>
-  </si>
-  <si>
-    <t>scenario year, e.g. 2025</t>
-  </si>
-  <si>
-    <t>Node name</t>
-  </si>
-  <si>
-    <t>&lt;country&gt;_&lt;grid&gt;_&lt;node_suffix&gt;</t>
-  </si>
-  <si>
-    <t>The code will construct node name with following formula</t>
-  </si>
-  <si>
-    <t>This allows constructing either national grids for e.g. electricity,</t>
-  </si>
-  <si>
-    <t>city-level grids for district heating, and other specific applications.</t>
-  </si>
-  <si>
-    <t>Raises errors from:</t>
-  </si>
-  <si>
-    <t>underscore in grid name</t>
-  </si>
-  <si>
-    <t>elec</t>
-  </si>
-  <si>
-    <t>Reserved grid names</t>
-  </si>
-  <si>
-    <t>for electricity demand</t>
-  </si>
-  <si>
     <t>Constant_share</t>
   </si>
   <si>
-    <t>Constant_share must be between [0-1]</t>
-  </si>
-  <si>
-    <t>Share of the annual demand that is constant at every hour. Accepts values [0-1]</t>
-  </si>
-  <si>
-    <t>heat</t>
-  </si>
-  <si>
     <t>TWh/year</t>
-  </si>
-  <si>
-    <t>Annual demand in TWh</t>
-  </si>
-  <si>
-    <t>for district heating</t>
-  </si>
-  <si>
-    <t>Processing</t>
-  </si>
-  <si>
-    <t>A = annual_demand * (1 - constant_share)</t>
-  </si>
-  <si>
-    <t>x = hourly profile</t>
-  </si>
-  <si>
-    <t>B = annual_demand * constant_share / 8760</t>
-  </si>
-  <si>
-    <t>Calculate hourly demands = Ax + B, where</t>
-  </si>
-  <si>
-    <t>Electricity has national profiles read from TYNDP scenarios</t>
-  </si>
-  <si>
-    <t>DH has national profiles from outdoor temperature data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          1. Python code reads only sheets start with "demands_" from each listed annual demands file.</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>grid</t>
-  </si>
-  <si>
-    <t>node_suffix</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>constant_share</t>
-  </si>
-  <si>
-    <t>Duplicate entries in any of the sheets</t>
   </si>
   <si>
     <t>steam</t>
@@ -248,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -268,12 +146,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -337,9 +209,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -360,7 +232,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -370,8 +242,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,212 +419,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3E3B46F-1155-4F9C-A4E0-671EDFFC1ADF}">
-  <sheetPr>
-    <tabColor theme="0"/>
-  </sheetPr>
-  <dimension ref="A4:R45"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="2" width="9.140625" style="14"/>
-    <col min="3" max="3" width="14.42578125" style="14" customWidth="1"/>
-    <col min="4" max="18" width="9.140625" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C12" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C15" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C16" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C17" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C18" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C21" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C26" s="14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C27" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C28" s="14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C29" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C31" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="C32" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C36" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C37" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C39" s="14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C40" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B42" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C43" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C44" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="C45" s="14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -784,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1221,7 +885,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -1241,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -1261,7 +925,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
